--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -754,8 +755,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -822,8 +826,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -890,8 +897,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -958,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -984,59 +997,60 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E12" s="3">
         <v>88300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>48600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>40600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>42200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>43800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>46100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>45200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>44800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7100</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1052,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1120,8 +1137,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1129,29 +1149,29 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>5000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-42800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1167,8 +1187,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1188,8 +1208,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1256,8 +1279,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1279,59 +1305,60 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E17" s="3">
         <v>103900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>65000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>54200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>63500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>48200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>34800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,8 +1374,11 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1356,50 +1386,50 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-65000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-51800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-54200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-63500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-57900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-48200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-55100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-50300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-40200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-34800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1415,8 +1445,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1441,8 +1474,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1450,22 +1484,22 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F20" s="3">
         <v>4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
       </c>
       <c r="I20" s="3">
         <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1477,23 +1511,23 @@
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,8 +1543,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1518,50 +1555,50 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-99100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-60500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-48200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-51900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-62700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-57100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-47900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-54900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-50200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-39900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1614,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1645,59 +1685,62 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-99500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-60800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-48500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-52300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-63000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-57500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-48100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-55000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-50200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-34600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,58 +1756,61 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1772,8 +1818,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1781,8 +1827,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1849,59 +1898,62 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-98900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-61000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-48200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-52100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-63100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-57500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-48300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-55100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-50400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-40400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8700</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,59 +1969,62 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-112500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-63200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-55000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-54400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-68400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-59100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-50100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-49900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-40300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1985,8 +2040,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2053,8 +2111,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2121,8 +2182,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2189,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2257,8 +2324,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2266,22 +2336,22 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
       </c>
       <c r="I32" s="3">
         <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2293,23 +2363,23 @@
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,59 +2395,62 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-112500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-63200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-55000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-54400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-68400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-59100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-50100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-49900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-40300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2393,8 +2466,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2461,59 +2537,62 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-112500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-63200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-55000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-54400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-68400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-59100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-50100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-49900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-40300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2529,64 +2608,67 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2602,8 +2684,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2628,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2654,56 +2740,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E41" s="3">
         <v>266600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>55100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>55000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>96000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>63700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2722,53 +2809,56 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>405900</v>
+      </c>
+      <c r="E42" s="3">
         <v>286400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>356200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>394300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>379200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>400100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>258800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>280200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>326000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>201700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>269400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>283600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>274900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>137200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2781,8 +2871,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2790,20 +2880,23 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,23 +2906,23 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>100</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
@@ -2837,8 +2930,8 @@
       <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>100</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -2849,8 +2942,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2858,8 +2951,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2926,56 +3022,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E45" s="3">
         <v>9100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>5200</v>
       </c>
       <c r="P45" s="3">
         <v>5200</v>
       </c>
       <c r="Q45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="R45" s="3">
         <v>2200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2985,8 +3084,8 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -2994,56 +3093,59 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>528300</v>
+      </c>
+      <c r="E46" s="3">
         <v>563900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>410200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>451900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>433900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>467600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>301300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>350800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>377600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>259400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>306400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>345100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>372700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>238500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>66000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3155,8 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W46" s="3">
         <v>0</v>
@@ -3062,8 +3164,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3071,29 +3176,29 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>18900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>30400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>35700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>37500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3109,8 +3214,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3130,56 +3235,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E48" s="3">
         <v>43200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>52800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>3400</v>
       </c>
       <c r="M48" s="3">
         <v>3400</v>
       </c>
       <c r="N48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O48" s="3">
         <v>3600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3189,8 +3297,8 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3198,8 +3306,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3228,7 +3339,7 @@
         <v>3700</v>
       </c>
       <c r="L49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="M49" s="3">
         <v>12500</v>
@@ -3245,8 +3356,8 @@
       <c r="Q49" s="3">
         <v>12500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>12500</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3257,8 +3368,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3266,8 +3377,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3334,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3402,56 +3519,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E52" s="3">
         <v>10500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,8 +3581,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3470,8 +3590,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3538,56 +3661,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>585700</v>
+      </c>
+      <c r="E54" s="3">
         <v>621400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>489300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>539300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>529200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>567900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>405700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>454500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>435100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>284000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>328400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>365600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>393200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>257200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>87600</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,8 +3732,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3632,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3658,56 +3788,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E57" s="3">
         <v>12300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>8300</v>
       </c>
       <c r="M57" s="3">
         <v>8300</v>
       </c>
       <c r="N57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="O57" s="3">
         <v>8700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3848,8 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -3726,8 +3857,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3794,56 +3928,59 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E59" s="3">
         <v>39500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>45400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3853,8 +3990,8 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -3862,56 +3999,59 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E60" s="3">
         <v>51800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>56400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>48600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3921,8 +4061,8 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
@@ -3930,8 +4070,11 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3998,56 +4141,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E62" s="3">
         <v>46400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>47300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>46400</v>
       </c>
       <c r="H62" s="3">
         <v>46400</v>
       </c>
       <c r="I62" s="3">
+        <v>46400</v>
+      </c>
+      <c r="J62" s="3">
         <v>46500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4057,8 +4203,8 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4066,8 +4212,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4134,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4202,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4270,56 +4425,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E66" s="3">
         <v>98300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>103900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>105500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>95400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>90400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>90600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>41600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>60000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>52200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>44000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4338,8 +4496,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4364,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4432,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4500,8 +4665,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4545,11 +4713,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>155900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4568,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4636,56 +4807,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-827600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-772100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-659600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-596400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-541400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-487000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-418600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-359600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-309500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-305300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-250700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-160500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-99100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,8 +4878,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4772,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4840,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4908,56 +5091,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E76" s="3">
         <v>523100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>385500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>433800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>428500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>472500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>315300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>364000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>393400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>223800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>268400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>308600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>341100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>213200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-95900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4967,8 +5153,8 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W76" s="3">
         <v>0</v>
@@ -4976,8 +5162,11 @@
       <c r="X76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5044,64 +5233,67 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5117,59 +5309,62 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-112500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-63200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-55000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-54400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-68400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-59100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-50100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-49900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-40300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5185,8 +5380,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5211,8 +5409,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5220,7 +5419,7 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
@@ -5229,16 +5428,16 @@
         <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
       </c>
       <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -5247,19 +5446,19 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -5270,8 +5469,8 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5279,8 +5478,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5347,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5415,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5483,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5551,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5619,56 +5833,59 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-79300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-49300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-33200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-43000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-50200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-33500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-46100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-27400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-20600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5678,8 +5895,8 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -5687,8 +5904,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5713,55 +5933,56 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-2700</v>
       </c>
       <c r="K91" s="3">
         <v>-2700</v>
       </c>
       <c r="L91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5772,8 +5993,8 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5781,8 +6002,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5849,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5917,55 +6144,58 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-117500</v>
+      </c>
+      <c r="E94" s="3">
         <v>72900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>42100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>20000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-142100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>43300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-141400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>66600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>13500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-137900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-137300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5976,8 +6206,8 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5985,8 +6215,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6011,8 +6244,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6079,8 +6313,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6147,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6215,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6283,56 +6526,59 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>236600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>49700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>209500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>166600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>155900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>191700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13500</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6342,8 +6588,8 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -6351,8 +6597,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6419,56 +6668,59 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-155800</v>
+      </c>
+      <c r="E102" s="3">
         <v>230300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>20200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-24000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-37600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>32400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6478,13 +6730,16 @@
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,96 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -758,31 +759,37 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="D8" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -829,8 +836,14 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -900,8 +913,14 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -971,8 +990,14 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,65 +1023,67 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>51600</v>
+      </c>
+      <c r="F12" s="3">
         <v>46800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>88300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>48600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>40600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>42200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>43800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>46100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>38400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>45200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>44800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>38400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>29500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>24700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>17500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>13300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>7100</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1069,8 +1096,14 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,44 +1173,50 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>5000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-42800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,11 +1229,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1211,8 +1250,14 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1282,8 +1327,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,65 +1357,67 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>67900</v>
+      </c>
+      <c r="F17" s="3">
         <v>62700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>103900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>65000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>51800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>54200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>63500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>57900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>48200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>11300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>55100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>50300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>40200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>34800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>27400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8700</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1377,65 +1430,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-103900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-65000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-51800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-54200</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-63500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-57900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-48200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-55100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-50300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-40200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-34800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-27400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-16400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-8700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1448,8 +1507,14 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,37 +1540,39 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1514,25 +1581,25 @@
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>300</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>100</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1546,65 +1613,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-99100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-60500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-48200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-51900</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-62700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-57100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-47900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-11100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-54900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-50200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-39900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-27300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-16200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-8600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,8 +1690,14 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1688,65 +1767,71 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-55500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-99500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-60800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-48500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-52300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-63000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-57500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-48100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-11200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-55000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-50200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-39900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-27300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-16200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-8700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1759,79 +1844,91 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,65 +1998,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-55500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-98900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-61000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-48200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-52100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-63100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-57500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-48300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-10500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-55100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-50400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-40400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-27300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-16200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-8700</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1972,65 +2075,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-55500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-112500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-63200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-55000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-54400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-68400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-59100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-50100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-54600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-49900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-40300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-26900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-16100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-8300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,8 +2152,14 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2229,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2185,8 +2306,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2383,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,37 +2460,43 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -2366,25 +2505,25 @@
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-100</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2398,65 +2537,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-55500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-112500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-63200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-55000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-54400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-68400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-59100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-50100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-54600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-49900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-40300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-26900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-16100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2614,14 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,65 +2691,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-55500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-112500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-63200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-55000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-54400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-68400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-59100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-50100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-54600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-49900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-40300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-26900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-16100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,70 +2768,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2850,14 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2883,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,62 +2912,64 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F41" s="3">
         <v>110800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>266600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>36300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>43100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>42600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>55100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>59700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>40800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>49200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>29000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>55000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>92600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>96000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>63700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2812,59 +2985,65 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>451400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>454900</v>
+      </c>
+      <c r="F42" s="3">
         <v>405900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>286400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>356200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>394300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>379200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>400100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>258800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>280200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>326000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>201700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>269400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>283600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>274900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>137200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2874,70 +3053,76 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F43" s="3">
         <v>1900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
-      </c>
-      <c r="P43" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>100</v>
       </c>
       <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>100</v>
+      </c>
+      <c r="T43" s="3">
+        <v>100</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -2945,17 +3130,23 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3025,186 +3216,204 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F45" s="3">
         <v>9700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>9100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>14600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>12400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>11900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>10900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>7700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>6200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>5200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>5200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>503800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>496700</v>
+      </c>
+      <c r="F46" s="3">
         <v>528300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>563900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>410200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>451900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>433900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>467600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>301300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>350800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>377600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>259400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>306400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>345100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>372700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>238500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>66000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3">
-        <v>0</v>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>18900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>21200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>28000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>30400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>35700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>37500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>39300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,11 +3426,11 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3238,79 +3447,91 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F48" s="3">
         <v>42600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>43200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>44400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>50100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>50700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>51500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>52100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>52800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3342,10 +3563,10 @@
         <v>3700</v>
       </c>
       <c r="M49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="N49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="O49" s="3">
         <v>12500</v>
@@ -3359,11 +3580,11 @@
       <c r="R49" s="3">
         <v>12500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>12500</v>
+      </c>
+      <c r="T49" s="3">
+        <v>12500</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3371,17 +3592,23 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3678,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,79 +3755,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F52" s="3">
         <v>11100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>10500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>12100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>12400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>12900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>14600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>9700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>9100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>6100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>5600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>6300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,62 +3909,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>557500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>551700</v>
+      </c>
+      <c r="F54" s="3">
         <v>585700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>621400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>489300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>539300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>529200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>567900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>405700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>454500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>435100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>284000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>328400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>365600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>393200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>257200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>87600</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3735,8 +3986,14 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +4019,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,79 +4048,87 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F57" s="3">
         <v>14300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>12300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>12800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>11200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>13200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>7000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3931,150 +4198,168 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>54400</v>
+      </c>
+      <c r="F59" s="3">
         <v>44700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>39500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>43500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>45400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>44200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>36600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>30300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>32400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>31400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>25300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>24500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>19900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>18500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>11400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>69400</v>
+      </c>
+      <c r="F60" s="3">
         <v>58900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>51800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>56400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>56600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>54100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>48600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>43500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>43900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>39400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>33600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>32800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>28600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>23900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>15600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>16900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
-      <c r="X60" s="3">
-        <v>0</v>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4144,79 +4429,91 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E62" s="3">
         <v>44900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>44900</v>
+      </c>
+      <c r="G62" s="3">
         <v>46400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>47300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>48600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>46400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>46400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>46500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>46100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4583,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4660,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,62 +4737,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>103900</v>
+        <v>98700</v>
       </c>
       <c r="E66" s="3">
-        <v>98300</v>
+        <v>114400</v>
       </c>
       <c r="F66" s="3">
         <v>103900</v>
       </c>
       <c r="G66" s="3">
+        <v>98300</v>
+      </c>
+      <c r="H66" s="3">
+        <v>103900</v>
+      </c>
+      <c r="I66" s="3">
         <v>105500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>100700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>95400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>90400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>90600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>41600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>60100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>60000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>57000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>52200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>44000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>27600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4499,8 +4814,14 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4847,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4920,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,8 +4997,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4716,14 +5051,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>155900</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4739,8 +5074,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,62 +5151,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-878500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-888600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-827600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-772100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-659600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-596400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-541400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-487000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-418600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-359600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-309500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-305300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-250700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-200800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-160500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-126000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-99100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4881,8 +5228,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5305,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5382,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,79 +5459,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>458800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>437300</v>
+      </c>
+      <c r="F76" s="3">
         <v>481800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>523100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>385500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>433800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>428500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>472500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>315300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>364000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>393400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>223800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>268400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>308600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>341100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>213200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-95900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3">
-        <v>0</v>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,70 +5613,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5312,65 +5695,71 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-55500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-112500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-63200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-55000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-54400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-68400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-59100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-50100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-54600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-49900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-40300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-34600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-26900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-16100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5383,8 +5772,14 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,8 +5805,10 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5422,34 +5819,34 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
       </c>
       <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -5458,13 +5855,13 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5472,17 +5869,23 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5955,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +6032,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +6109,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +6186,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,79 +6263,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-40600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-38700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-79300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-49300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-37300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-33200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-43000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-50200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-37000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-33500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-46100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-37500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-27400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-22000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-16900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,61 +6373,63 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5996,17 +6437,23 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6523,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,61 +6600,67 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-117500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>72900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>42100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-11900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>20000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-142100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>19800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>43300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-141400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>66600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>13500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-137900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-137300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -6209,17 +6668,23 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,8 +6710,10 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6316,8 +6783,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6860,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6937,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,79 +7014,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>236600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>49700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>209500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>12300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>166600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>155900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>191700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>13500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6671,75 +7168,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-82700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-155800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>230300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-6800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-12600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>24300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-29100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>18500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-8400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>20200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-24000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-37600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>32400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,100 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -765,17 +766,20 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>40600</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,8 +795,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -842,8 +846,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -919,8 +926,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -996,8 +1006,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,68 +1038,69 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E12" s="3">
         <v>49600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>51600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>46800</v>
       </c>
-      <c r="G12" s="3">
-        <v>88300</v>
-      </c>
       <c r="H12" s="3">
+        <v>42700</v>
+      </c>
+      <c r="I12" s="3">
         <v>48600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>40600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>42200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>43800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>46100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>44800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>38400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7100</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1102,8 +1116,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1179,16 +1196,19 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1197,29 +1217,29 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>45600</v>
+      </c>
+      <c r="I14" s="3">
         <v>5000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-42800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1235,8 +1255,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1256,8 +1276,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1333,8 +1356,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1359,68 +1385,69 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E17" s="3">
         <v>65300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>67900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>62700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>103900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>65000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>51800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8700</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,17 +1463,20 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24700</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1462,42 +1492,42 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-63500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-57900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-48200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-55100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-34800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-27400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,8 +1543,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,17 +1575,18 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>34900</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1568,14 +1602,14 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>400</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>400</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
@@ -1587,23 +1621,23 @@
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,17 +1653,20 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>10500</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,42 +1682,42 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-62700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-57100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-47900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-54900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-39900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-34600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-27300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,8 +1733,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1773,68 +1813,71 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-61100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-55500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-99500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-60800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-48500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-52300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-63000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-57500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-48100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-55000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-39900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-34600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8700</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1850,67 +1893,70 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1918,8 +1964,8 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -1927,8 +1973,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2004,68 +2053,71 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E26" s="3">
         <v>10000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-60900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-55500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-98900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-61000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-48200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-52100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-63100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-57500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-48300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-55100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-50400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-40400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-34700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-27300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8700</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,68 +2133,71 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E27" s="3">
         <v>10100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-60900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-55500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-112500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-63200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-55000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-54400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-68400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-59100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-50100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-40300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-34600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-26900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2158,8 +2213,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2235,8 +2293,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2312,8 +2373,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2389,8 +2453,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2466,17 +2533,20 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-34900</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2492,14 +2562,14 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>-400</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>-400</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
@@ -2511,23 +2581,23 @@
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,68 +2613,71 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E33" s="3">
         <v>10100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-60900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-55500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-112500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-63200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-55000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-54400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-68400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-59100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-50100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-40300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-34600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-26900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,8 +2693,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2697,68 +2773,71 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E35" s="3">
         <v>10100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-60900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-55500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-112500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-63200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-55000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-54400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-68400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-59100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-50100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-40300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-34600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-26900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,73 +2853,76 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2938,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2885,8 +2970,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2914,65 +3000,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E41" s="3">
         <v>37600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>266600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>59700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>40800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>29000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>55000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>96000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>63700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2991,62 +3078,65 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>389400</v>
+      </c>
+      <c r="E42" s="3">
         <v>451400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>454900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>405900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>286400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>356200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>394300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>379200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>400100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>258800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>280200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>326000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>201700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>269400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>283600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>274900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>137200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,8 +3149,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3068,29 +3158,32 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,23 +3193,23 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
-      </c>
-      <c r="R43" s="3">
-        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
@@ -3124,8 +3217,8 @@
       <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>100</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -3136,8 +3229,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3145,8 +3238,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3222,65 +3318,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="3">
         <v>11700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>12200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>5200</v>
       </c>
       <c r="S45" s="3">
         <v>5200</v>
       </c>
       <c r="T45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="U45" s="3">
         <v>2200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3290,8 +3389,8 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -3299,65 +3398,68 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>439600</v>
+      </c>
+      <c r="E46" s="3">
         <v>503800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>496700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>528300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>563900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>410200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>451900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>433900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>467600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>301300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>350800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>377600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>259400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>306400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>345100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>372700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>238500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>66000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3367,8 +3469,8 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y46" s="3">
-        <v>0</v>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z46" s="3">
         <v>0</v>
@@ -3376,16 +3478,19 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
@@ -3394,29 +3499,29 @@
         <v>0</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>18900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>21200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>30400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>35700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>37500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39300</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3432,8 +3537,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3453,65 +3558,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E48" s="3">
         <v>40400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>52100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>3400</v>
       </c>
       <c r="P48" s="3">
         <v>3400</v>
       </c>
       <c r="Q48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R48" s="3">
         <v>3600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,8 +3629,8 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -3530,8 +3638,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3569,7 +3680,7 @@
         <v>3700</v>
       </c>
       <c r="O49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="P49" s="3">
         <v>12500</v>
@@ -3586,8 +3697,8 @@
       <c r="T49" s="3">
         <v>12500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>12500</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3598,8 +3709,8 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3607,8 +3718,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3684,8 +3798,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3761,8 +3878,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3773,53 +3893,53 @@
         <v>9500</v>
       </c>
       <c r="F52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="G52" s="3">
         <v>11100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3829,8 +3949,8 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -3838,8 +3958,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3915,65 +4038,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>491700</v>
+      </c>
+      <c r="E54" s="3">
         <v>557500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>551700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>585700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>621400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>489300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>539300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>529200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>567900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>405700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>454500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>435100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>284000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>328400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>365600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>393200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>257200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>87600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3992,8 +4118,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4021,8 +4150,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4050,65 +4180,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E57" s="3">
         <v>10500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>8300</v>
       </c>
       <c r="P57" s="3">
         <v>8300</v>
       </c>
       <c r="Q57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="R57" s="3">
         <v>8700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4118,8 +4249,8 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
@@ -4127,8 +4258,11 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4204,65 +4338,68 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E59" s="3">
         <v>44300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>54400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>39500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>43500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>45400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>44200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>36600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>30300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>32400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9900</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4272,8 +4409,8 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4281,65 +4418,68 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E60" s="3">
         <v>54800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>69400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>58900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>51800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>54100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>48600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>43500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>39400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>32800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>15600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>16900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4349,8 +4489,8 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y60" s="3">
-        <v>0</v>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z60" s="3">
         <v>0</v>
@@ -4358,8 +4498,11 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4435,65 +4578,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E62" s="3">
         <v>43900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>44900</v>
       </c>
       <c r="F62" s="3">
         <v>44900</v>
       </c>
       <c r="G62" s="3">
+        <v>44900</v>
+      </c>
+      <c r="H62" s="3">
         <v>46400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>48600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>46400</v>
       </c>
       <c r="K62" s="3">
         <v>46400</v>
       </c>
       <c r="L62" s="3">
+        <v>46400</v>
+      </c>
+      <c r="M62" s="3">
         <v>46500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4649,8 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4512,8 +4658,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4589,8 +4738,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4666,8 +4818,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4743,65 +4898,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E66" s="3">
         <v>98700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>114400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>103900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>98300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>103900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>105500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>95400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>90400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>60100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>52200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>44000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4820,8 +4978,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4849,8 +5010,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4926,8 +5088,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5003,8 +5168,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5057,11 +5225,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>155900</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5080,8 +5248,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5157,65 +5328,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-966800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-878500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-888600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-827600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-772100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-659600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-596400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-541400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-487000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-418600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-359600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-309500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-305300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-250700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-160500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-126000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-99100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5234,8 +5408,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5311,8 +5488,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5388,8 +5568,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5465,65 +5648,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>382600</v>
+      </c>
+      <c r="E76" s="3">
         <v>458800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>437300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>481800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>523100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>385500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>433800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>428500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>472500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>315300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>364000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>393400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>223800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>268400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>308600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>341100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>213200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-95900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5533,8 +5719,8 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z76" s="3">
         <v>0</v>
@@ -5542,8 +5728,11 @@
       <c r="AA76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5619,73 +5808,76 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5701,68 +5893,71 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="E81" s="3">
         <v>10100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-60900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-55500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-112500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-63200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-55000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-54400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-68400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-59100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-50100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-40300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-34600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-26900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5778,8 +5973,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5807,8 +6005,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5825,7 +6024,7 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -5834,16 +6033,16 @@
         <v>400</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -5852,19 +6051,19 @@
         <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5875,8 +6074,8 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5884,8 +6083,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5961,8 +6163,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6038,8 +6243,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6115,8 +6323,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6192,8 +6403,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6269,65 +6483,68 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-52000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-40600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-38700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-79300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-49300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-33200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-43000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-50200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-33500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-46100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-27400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-20600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-22000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6337,8 +6554,8 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -6346,8 +6563,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6375,64 +6595,65 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-2700</v>
       </c>
       <c r="N91" s="3">
         <v>-2700</v>
       </c>
       <c r="O91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -6443,8 +6664,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6452,8 +6673,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6529,8 +6753,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6606,64 +6833,67 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E94" s="3">
         <v>61500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-117500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>72900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>42100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>20000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-142100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>43300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-141400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>66600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>13500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-137900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-137300</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6674,8 +6904,8 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6683,8 +6913,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6712,8 +6945,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6789,8 +7023,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6866,8 +7103,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6943,8 +7183,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7020,8 +7263,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7032,53 +7278,53 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>236600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>49700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>209500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>166600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>155900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>191700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13500</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7088,8 +7334,8 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7097,8 +7343,11 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7174,65 +7423,68 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>9600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-82700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-155800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>230300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>24300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>18500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-37600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>32400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7242,13 +7494,16 @@
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,104 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -769,20 +770,23 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>40600</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
@@ -798,8 +802,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -849,8 +853,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -929,8 +936,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -940,8 +950,8 @@
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="F10" s="3">
+        <v>40600</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -1009,8 +1019,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,71 +1052,72 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E12" s="3">
         <v>48400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>49600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>51600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>46800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>42700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>40600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>42200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>43800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>46100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>38400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>45200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>44800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>38400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>29500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7100</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1119,8 +1133,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1199,50 +1216,53 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>45600</v>
       </c>
-      <c r="I14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-42800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,8 +1278,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1279,31 +1299,34 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1359,8 +1382,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1386,71 +1412,72 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E17" s="3">
         <v>65100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>65300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>67900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>62700</v>
       </c>
-      <c r="H17" s="3">
-        <v>103900</v>
-      </c>
       <c r="I17" s="3">
+        <v>58300</v>
+      </c>
+      <c r="J17" s="3">
         <v>65000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>51800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>57900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8700</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,71 +1493,74 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-51400</v>
       </c>
       <c r="E18" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-65100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-67900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-62700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-58300</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-65000</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-63500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-57900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-48200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-50300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-34800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-27400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-16400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1546,8 +1576,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1576,43 +1609,44 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>34900</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2300</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>400</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
@@ -1624,23 +1658,23 @@
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,71 +1690,74 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-51100</v>
       </c>
       <c r="E21" s="3">
-        <v>10500</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-64800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-71700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-66900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-62700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-57100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-47900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-54900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-50200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-39900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-34600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-27300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1736,31 +1773,34 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1816,71 +1856,74 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-88000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-61100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-99500</v>
-      </c>
       <c r="I23" s="3">
-        <v>-60800</v>
+        <v>-113200</v>
       </c>
       <c r="J23" s="3">
+        <v>-63200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-48500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-52300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-63000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-57500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-48100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-50200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-39900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-34600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1896,70 +1939,73 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1967,8 +2013,8 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -1976,8 +2022,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2056,71 +2105,74 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-88300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-60900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-55500</v>
       </c>
-      <c r="H26" s="3">
-        <v>-98900</v>
-      </c>
       <c r="I26" s="3">
-        <v>-61000</v>
+        <v>-112600</v>
       </c>
       <c r="J26" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-48200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-63100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-57500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-48300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-50400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-40400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-34700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-27300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8700</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2136,71 +2188,74 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-88300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-60900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-55500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-112500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-63200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-55000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-68400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-59100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-50100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-49900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-40300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-34600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-26900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2216,8 +2271,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2296,8 +2354,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2376,8 +2437,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2456,8 +2520,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2536,43 +2603,46 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>-34900</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-2300</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>-400</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
@@ -2584,23 +2654,23 @@
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2616,71 +2686,74 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-88300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-60900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-55500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-112500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-63200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-55000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-68400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-59100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-50100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-49900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-40300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-34600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-26900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2696,8 +2769,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2776,71 +2852,74 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-88300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-60900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-55500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-112500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-63200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-55000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-68400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-59100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-50100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-49900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-40300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-34600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-26900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,76 +2935,79 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2941,8 +3023,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2971,8 +3056,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3001,68 +3087,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E41" s="3">
         <v>37000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>266600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>59700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>40800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>55000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>92600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>96000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>63700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3081,65 +3168,68 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>349900</v>
+      </c>
+      <c r="E42" s="3">
         <v>389400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>451400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>454900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>405900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>286400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>356200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>394300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>379200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>400100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>258800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>280200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>326000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>201700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>269400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>283600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>274900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>137200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3242,8 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3161,28 +3251,31 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>3300</v>
-      </c>
-      <c r="E43" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I43" s="3">
-        <v>8300</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -3196,23 +3289,23 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
-      </c>
-      <c r="S43" s="3">
-        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
@@ -3220,8 +3313,8 @@
       <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+      <c r="V43" s="3">
+        <v>100</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
@@ -3232,8 +3325,8 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -3241,31 +3334,34 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3321,68 +3417,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>10000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>11700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>9100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>14600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6200</v>
-      </c>
-      <c r="S45" s="3">
-        <v>5200</v>
       </c>
       <c r="T45" s="3">
         <v>5200</v>
       </c>
       <c r="U45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="V45" s="3">
         <v>2200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3392,8 +3491,8 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -3401,68 +3500,71 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>400300</v>
+      </c>
+      <c r="E46" s="3">
         <v>439600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>503800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>496700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>528300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>563900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>410200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>451900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>433900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>467600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>301300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>350800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>377600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>259400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>306400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>345100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>372700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>238500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>66000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3574,8 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA46" s="3">
         <v>0</v>
@@ -3481,8 +3583,11 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3492,39 +3597,39 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>18900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>21200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>30400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>35700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>37500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>39300</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3540,8 +3645,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3561,68 +3666,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E48" s="3">
         <v>38800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>52800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>3400</v>
       </c>
       <c r="Q48" s="3">
         <v>3400</v>
       </c>
       <c r="R48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S48" s="3">
         <v>3600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3632,8 +3740,8 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -3641,8 +3749,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3683,7 +3794,7 @@
         <v>3700</v>
       </c>
       <c r="P49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="Q49" s="3">
         <v>12500</v>
@@ -3700,8 +3811,8 @@
       <c r="U49" s="3">
         <v>12500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>12500</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3712,8 +3823,8 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -3721,8 +3832,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3801,8 +3915,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3881,13 +3998,16 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9500</v>
+        <v>8200</v>
       </c>
       <c r="E52" s="3">
         <v>9500</v>
@@ -3896,53 +4016,53 @@
         <v>9500</v>
       </c>
       <c r="G52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="H52" s="3">
         <v>11100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,8 +4072,8 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -3961,8 +4081,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4041,68 +4164,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>450700</v>
+      </c>
+      <c r="E54" s="3">
         <v>491700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>557500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>551700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>585700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>621400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>489300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>539300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>529200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>567900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>405700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>454500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>435100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>284000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>328400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>365600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>393200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>257200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>87600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4121,8 +4247,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4151,8 +4280,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4181,68 +4311,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
         <v>20400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>8300</v>
       </c>
       <c r="Q57" s="3">
         <v>8300</v>
       </c>
       <c r="R57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="S57" s="3">
         <v>8700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4383,8 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
@@ -4261,31 +4392,34 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4341,68 +4475,71 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>46300</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
-        <v>44300</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>54400</v>
+        <v>400</v>
       </c>
       <c r="G59" s="3">
-        <v>44700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>39500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>43500</v>
-      </c>
-      <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>45400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>36600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>30300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>32400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4549,8 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -4421,68 +4558,71 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E60" s="3">
         <v>66700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>54800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>58900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>51800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>56400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>56600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>54100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>48600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16900</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4492,8 +4632,8 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z60" s="3">
-        <v>0</v>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA60" s="3">
         <v>0</v>
@@ -4501,31 +4641,34 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>41300</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>42600</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>43300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>44800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4581,68 +4724,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>42400</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
-        <v>43900</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="3">
-        <v>44900</v>
+        <v>1300</v>
       </c>
       <c r="G62" s="3">
-        <v>44900</v>
+        <v>1800</v>
       </c>
       <c r="H62" s="3">
-        <v>46400</v>
+        <v>1600</v>
       </c>
       <c r="I62" s="3">
-        <v>47300</v>
+        <v>2400</v>
       </c>
       <c r="J62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K62" s="3">
         <v>48600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>46400</v>
       </c>
       <c r="L62" s="3">
         <v>46400</v>
       </c>
       <c r="M62" s="3">
+        <v>46400</v>
+      </c>
+      <c r="N62" s="3">
         <v>46500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4652,8 +4798,8 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
@@ -4661,8 +4807,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4741,8 +4890,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4821,8 +4973,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4901,68 +5056,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>96300</v>
+      </c>
+      <c r="E66" s="3">
         <v>109100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98700</v>
       </c>
-      <c r="F66" s="3">
-        <v>114400</v>
-      </c>
       <c r="G66" s="3">
-        <v>103900</v>
+        <v>114300</v>
       </c>
       <c r="H66" s="3">
-        <v>98300</v>
+        <v>103800</v>
       </c>
       <c r="I66" s="3">
-        <v>103900</v>
+        <v>98200</v>
       </c>
       <c r="J66" s="3">
+        <v>103700</v>
+      </c>
+      <c r="K66" s="3">
         <v>105500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>95400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>90600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>60100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>52200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>44000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4981,8 +5139,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5011,8 +5172,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5091,8 +5253,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5171,8 +5336,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5228,11 +5396,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>155900</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5251,8 +5419,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5331,68 +5502,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1006900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-966800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-878500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-888600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-827600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-772100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-659600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-596400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-541400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-487000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-418600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-359600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-309500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-305300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-250700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-160500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-126000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-99100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5411,8 +5585,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5491,8 +5668,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5571,8 +5751,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5651,68 +5834,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>354300</v>
+      </c>
+      <c r="E76" s="3">
         <v>382600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>458800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>437300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>481800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>523100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>385500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>433800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>428500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>472500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>315300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>364000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>393400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>223800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>268400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>308600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>341100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>213200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-95900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,8 +5908,8 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA76" s="3">
         <v>0</v>
@@ -5731,8 +5917,11 @@
       <c r="AB76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5811,76 +6000,79 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5896,71 +6088,74 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-88300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-60900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-55500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-112500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-63200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-55000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-68400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-59100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-50100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-54600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-49900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-40300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-34600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-26900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,8 +6171,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6006,8 +6204,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6018,34 +6217,34 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
+        <v>400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>400</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
       </c>
       <c r="L83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
       </c>
       <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>100</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -6054,19 +6253,19 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -6077,8 +6276,8 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6086,8 +6285,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6166,8 +6368,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6246,8 +6451,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6326,8 +6534,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6406,8 +6617,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6486,68 +6700,71 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-35100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-52000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-40600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-38700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-79300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-49300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-33200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-43000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-50200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-33500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-46100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-27400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-20600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-22000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16900</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6557,8 +6774,8 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -6566,8 +6783,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6596,67 +6816,68 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2700</v>
       </c>
       <c r="O91" s="3">
         <v>-2700</v>
       </c>
       <c r="P91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6667,8 +6888,8 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6676,8 +6897,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6756,8 +6980,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6836,67 +7063,70 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E94" s="3">
         <v>34500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>61500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-117500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>72900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>42100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-142100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>43300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-141400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>66600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>13500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-137900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-137300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6907,8 +7137,8 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6916,8 +7146,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6946,31 +7179,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7026,8 +7260,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7106,8 +7343,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7186,8 +7426,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7266,13 +7509,16 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -7281,53 +7527,53 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>236600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>49700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>209500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>166600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>155900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>191700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>13500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7337,8 +7583,8 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -7346,31 +7592,34 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7426,68 +7675,71 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-82700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-155800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>230300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>24300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-29100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-24000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-37600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7497,13 +7749,16 @@
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,111 +656,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -773,26 +774,32 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>40600</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -805,11 +812,11 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -856,8 +863,14 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -939,26 +952,32 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>40600</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1041,14 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1053,77 +1078,79 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F12" s="3">
         <v>36800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>48400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>49600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>51600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>46800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>42700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>48600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>40600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>42200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>43800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>46100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>38400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>45200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>44800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>38400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>29500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>24700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>17500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>13300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>7100</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1136,8 +1163,14 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1219,56 +1252,62 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>10500</v>
       </c>
       <c r="E14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>22900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-13200</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>45600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-42800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,11 +1320,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1302,8 +1341,14 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1326,14 +1371,14 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
+        <v>300</v>
+      </c>
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1385,8 +1430,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1413,77 +1464,79 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F17" s="3">
         <v>51400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>65100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>65300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>67900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>62700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>58300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>65000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>51800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>54200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>63500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>57900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>48200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>11300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>55100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>50300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>40200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>34800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>27400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>16400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>8700</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1496,77 +1549,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-51400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-65100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-24800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-67900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-62700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-58300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-65000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-63500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-57900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-48200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-55100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-50300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-40200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-34800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-27400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-16400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-8700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1638,14 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1610,8 +1675,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1624,35 +1691,35 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>13700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
@@ -1661,25 +1728,25 @@
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>300</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>100</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1693,77 +1760,83 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-51100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-64800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-24400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-67600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-62400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-71700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-66900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-62700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-57100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-47900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-54900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-50200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-39900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-34600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-27300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-16200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-8600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,8 +1849,14 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1802,11 +1881,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1859,77 +1938,83 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-40200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-88000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>10200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-61100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-55500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-113200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-63200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-48500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-52300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-63000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-57500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-48100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-55000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-50200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-39900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-34600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-27300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-16200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-8700</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1942,91 +2027,103 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2108,77 +2205,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-40200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-88300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-60900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-55500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-112600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-63300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-48200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-52100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-63100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-57500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-48300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-55100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-50400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-40400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-34700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-27300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-16200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-8700</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,77 +2294,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-40200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-88300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>10100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-60900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-55500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-112500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-63200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-55000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-54400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-68400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-59100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-50100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-54600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-49900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-40300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-34600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-26900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-16100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2274,8 +2383,14 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2357,8 +2472,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2440,8 +2561,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2523,8 +2650,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2606,8 +2739,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2620,35 +2759,35 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-13700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
@@ -2657,25 +2796,25 @@
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-100</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2689,77 +2828,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-40200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-88300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>10100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-60900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-55500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-112500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-63200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-55000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-54400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-68400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-59100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-50100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-54600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-49900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-40300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-34600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-26900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-16100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2917,14 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2855,77 +3006,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-40200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-88300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>10100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-60900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-55500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-112500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-63200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-55000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-54400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-68400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-59100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-50100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-54600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-49900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-40300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-34600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-26900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-16100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2938,82 +3095,88 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3189,14 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3057,8 +3226,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3088,74 +3259,76 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>33900</v>
+      </c>
+      <c r="F41" s="3">
         <v>41300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>37000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>37600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>28000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>110800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>266600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>36300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>43100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>42600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>55100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>30600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>59700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>40800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>49200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>29000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>55000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>92600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>96000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>63700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,71 +3344,77 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>290500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>337200</v>
+      </c>
+      <c r="F42" s="3">
         <v>349900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>389400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>451400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>454900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>405900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>286400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>356200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>394300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>379200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>400100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>258800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>280200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>326000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>201700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>269400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>283600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>274900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>137200</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,25 +3424,31 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>5000</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -3292,35 +3477,35 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>400</v>
-      </c>
-      <c r="T43" s="3">
-        <v>100</v>
-      </c>
-      <c r="U43" s="3">
-        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
+        <v>100</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
@@ -3328,17 +3513,23 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3363,11 +3554,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3420,8 +3611,14 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3446,148 +3643,160 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>14600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>12200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>12400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>11900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>10900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>10700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>7700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>6200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>5200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>5200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>386100</v>
+      </c>
+      <c r="F46" s="3">
         <v>400300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>439600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>503800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>496700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>528300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>563900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>410200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>451900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>433900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>467600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>301300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>350800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>377600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>259400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>306400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>345100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>372700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>238500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>66000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>0</v>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3609,33 +3818,33 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>18900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>21200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>28000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>30400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>35700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>37500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>39300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,11 +3857,11 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3669,99 +3878,111 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>37200</v>
+      </c>
+      <c r="F48" s="3">
         <v>38400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>38800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>40400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>41700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>42600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>43200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>44400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>50100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>50700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>51500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>52100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>52800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>3400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>2800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>3700</v>
@@ -3797,10 +4018,10 @@
         <v>3700</v>
       </c>
       <c r="Q49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="R49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="S49" s="3">
         <v>12500</v>
@@ -3814,11 +4035,11 @@
       <c r="V49" s="3">
         <v>12500</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>12500</v>
+      </c>
+      <c r="X49" s="3">
+        <v>12500</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -3826,17 +4047,23 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3918,8 +4145,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4001,91 +4234,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F52" s="3">
         <v>8200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>9500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>9500</v>
       </c>
       <c r="G52" s="3">
         <v>9500</v>
       </c>
       <c r="H52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J52" s="3">
         <v>11100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>10500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>12400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>12900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>14600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>12800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>9700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>9100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>8500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>6100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>4300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>5600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>6300</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4167,74 +4412,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>430300</v>
+      </c>
+      <c r="F54" s="3">
         <v>450700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>491700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>557500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>551700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>585700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>621400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>489300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>539300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>529200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>567900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>405700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>454500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>435100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>284000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>328400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>365600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>393200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>257200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>87600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4250,8 +4501,14 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4281,8 +4538,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4312,121 +4571,129 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F57" s="3">
         <v>8200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>20400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>14300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>12800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>9800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>13200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>8300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>8300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>8700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>4200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4478,204 +4745,222 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>45400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>44200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>36600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>30300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>32400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>31400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>25300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>24500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>19900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>18500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>11400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>9900</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>52700</v>
+      </c>
+      <c r="F60" s="3">
         <v>54900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>66700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>54800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>69400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>58900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>51800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>56400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>56600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>54100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>48600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>43500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>43900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>39400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>33600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>32800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>28600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>15600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>16900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>0</v>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>39600</v>
+      </c>
+      <c r="F61" s="3">
         <v>40500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>41300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>42600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>43200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>43300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>44000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>44800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4727,91 +5012,103 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>48600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>46400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>46400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>46500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>46100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4893,8 +5190,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4976,8 +5279,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5059,74 +5368,80 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>93200</v>
+      </c>
+      <c r="F66" s="3">
         <v>96300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>109100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>98700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>114300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>103800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>98200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>103700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>105500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>100700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>95400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>90400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>90600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>41600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>60100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>60000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>57000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>52200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>44000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>27600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5142,8 +5457,14 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5173,8 +5494,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5256,8 +5579,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5339,8 +5668,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5399,14 +5734,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>155900</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5422,8 +5757,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5505,74 +5846,80 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1102700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1054400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1006900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-966800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-878500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-888600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-827600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-772100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-659600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-596400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-541400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-487000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-418600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-359600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-309500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-305300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-250700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-200800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-160500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-126000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-99100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5588,8 +5935,14 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5671,8 +6024,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5754,8 +6113,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5837,91 +6202,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>295400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>337200</v>
+      </c>
+      <c r="F76" s="3">
         <v>354300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>382600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>458800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>437300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>481800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>523100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>385500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>433800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>428500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>472500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>315300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>364000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>393400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>223800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>268400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>308600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>341100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>213200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-95900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>0</v>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6003,82 +6380,88 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6091,77 +6474,83 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-40200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-88300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>10100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-60900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-55500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-112500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-63200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-55000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-54400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-68400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-59100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-50100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-54600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-49900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-40300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-34600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-26900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-16100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6174,8 +6563,14 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6205,8 +6600,10 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6217,46 +6614,46 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
       </c>
       <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>100</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -6265,13 +6662,13 @@
         <v>0</v>
       </c>
       <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -6279,17 +6676,23 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6371,8 +6774,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6454,8 +6863,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6537,8 +6952,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6620,8 +7041,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6703,91 +7130,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-44000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-35100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-52000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-40600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-38700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-79300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-49300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-37300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-33200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-43000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-50200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-37000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-33500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-46100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-37500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-27400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-20600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-22000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-16900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6817,16 +7256,18 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -6835,55 +7276,55 @@
         <v>-200</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -6891,17 +7332,23 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6983,8 +7430,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7066,73 +7519,79 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F94" s="3">
         <v>48200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>34500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>61500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-42100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-117500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>72900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>42100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-11900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>20000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-142100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>19800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>43300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-141400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>66600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>13500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-9600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-137900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-137300</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -7140,17 +7599,23 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7180,8 +7645,10 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7206,11 +7673,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7263,8 +7730,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7346,8 +7819,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7429,8 +7908,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7512,91 +7997,103 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>236600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>49700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>209500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>12300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>166600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>155900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>191700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>13500</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7621,11 +8118,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7678,87 +8175,99 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F102" s="3">
         <v>4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>9600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-82700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-155800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>230300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-12600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>24300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-29100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>18500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>20200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-24000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-37600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>32400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-3400</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,115 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -780,29 +781,32 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>26900</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>40600</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,8 +822,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -869,8 +873,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -958,29 +965,32 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>26900</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>40600</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1047,8 +1057,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1080,80 +1093,81 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E12" s="3">
         <v>27200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>48400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>49600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>51600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>46800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>42700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>48600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>40600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>42200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>43800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>46100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>38400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>45200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>44800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>38400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>29500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>17500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,8 +1183,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1258,59 +1275,62 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>10500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>22900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-4600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>45600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-42800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1326,8 +1346,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1347,13 +1367,16 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1377,11 +1400,11 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
+        <v>300</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1436,8 +1459,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1466,80 +1492,81 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E17" s="3">
         <v>37800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>73000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>65100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>65300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>67900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>62700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>58300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>65000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>50300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>27400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8700</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1555,80 +1582,83 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-46100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-51400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-65100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-24800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-67900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-62700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-58300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-65000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-63500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-57900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-48200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-55100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-50300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-34800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-27400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,8 +1674,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1677,8 +1710,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1697,32 +1731,32 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>13700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>400</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
         <v>400</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
@@ -1734,23 +1768,23 @@
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1766,80 +1800,83 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-37600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-45800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-51100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-64800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-24400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-67600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-62400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-71700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-66900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-62700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-57100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-47900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-54900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-50200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-39900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-34600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-27300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,8 +1892,11 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1887,8 +1927,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1944,80 +1984,83 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-47700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-40200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-88000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-61100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-55500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-113200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-63200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-48500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-52300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-63000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-57500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-48100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-55000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-50200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-39900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-34600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,79 +2076,82 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -2113,8 +2159,8 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2122,8 +2168,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2211,80 +2260,83 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-48300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-88300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-60900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-55500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-112600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-63300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-48200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-52100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-63100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-57500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-48300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-55100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-50400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-40400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-34700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-27300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2300,80 +2352,83 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-48300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-88300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-60900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-55500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-112500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-63200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-55000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-68400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-50100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-54600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-49900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-40300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-34600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-26900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,8 +2444,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2478,8 +2536,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2567,8 +2628,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2656,8 +2720,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2745,8 +2812,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2765,32 +2835,32 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-13700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>-400</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
         <v>-400</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
@@ -2802,23 +2872,23 @@
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,80 +2904,83 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-48300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-88300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-60900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-55500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-112500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-63200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-55000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-68400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-50100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-54600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-49900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-40300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-34600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-26900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,8 +2996,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3012,80 +3088,83 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-48300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-88300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-60900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-55500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-112500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-63200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-55000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-68400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-50100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-54600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-49900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-40300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-34600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-26900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,85 +3180,88 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3195,8 +3277,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3228,8 +3313,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3261,77 +3347,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E41" s="3">
         <v>41900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>28000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>110800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>266600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>43100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>55100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>55000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>92600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>96000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>63700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,74 +3437,77 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>265800</v>
+      </c>
+      <c r="E42" s="3">
         <v>290500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>337200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>349900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>389400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>451400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>454900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>405900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>286400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>356200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>394300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>379200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>400100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>258800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>280200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>326000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>201700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>269400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>283600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>274900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>137200</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3430,8 +3520,8 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3439,20 +3529,23 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>5000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,23 +3576,23 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
-      </c>
-      <c r="V43" s="3">
-        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
@@ -3507,8 +3600,8 @@
       <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
+      <c r="Y43" s="3">
+        <v>100</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
@@ -3519,8 +3612,8 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
@@ -3528,8 +3621,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3560,8 +3656,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3617,8 +3713,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3649,45 +3748,45 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>14600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6200</v>
-      </c>
-      <c r="V45" s="3">
-        <v>5200</v>
       </c>
       <c r="W45" s="3">
         <v>5200</v>
       </c>
       <c r="X45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Y45" s="3">
         <v>2200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3796,8 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -3706,77 +3805,80 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>311600</v>
+      </c>
+      <c r="E46" s="3">
         <v>342900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>386100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>439600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>503800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>496700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>528300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>563900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>410200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>451900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>433900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>467600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>301300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>350800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>377600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>259400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>306400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>345100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>372700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>238500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>66000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3786,8 +3888,8 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC46" s="3">
-        <v>0</v>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD46" s="3">
         <v>0</v>
@@ -3795,8 +3897,11 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3824,30 +3929,30 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>18900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>21200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>35700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>37500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>39300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3968,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3884,77 +3989,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E48" s="3">
         <v>35200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>52100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>52800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>3400</v>
       </c>
       <c r="T48" s="3">
         <v>3400</v>
       </c>
       <c r="U48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="V48" s="3">
         <v>3600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3964,8 +4072,8 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -3973,8 +4081,11 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3985,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
         <v>3700</v>
@@ -4024,7 +4135,7 @@
         <v>3700</v>
       </c>
       <c r="S49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="T49" s="3">
         <v>12500</v>
@@ -4041,8 +4152,8 @@
       <c r="X49" s="3">
         <v>12500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>12500</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
@@ -4053,8 +4164,8 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4062,8 +4173,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4151,8 +4265,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4240,22 +4357,25 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>9500</v>
       </c>
       <c r="H52" s="3">
         <v>9500</v>
@@ -4264,53 +4384,53 @@
         <v>9500</v>
       </c>
       <c r="J52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K52" s="3">
         <v>11100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4320,8 +4440,8 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -4329,8 +4449,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4418,77 +4541,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>351700</v>
+      </c>
+      <c r="E54" s="3">
         <v>384000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>430300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>450700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>491700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>557500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>551700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>585700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>621400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>489300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>539300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>529200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>567900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>405700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>454500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>435100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>284000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>328400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>365600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>393200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>257200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>87600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4507,8 +4633,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4540,8 +4669,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4573,77 +4703,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8000</v>
-      </c>
-      <c r="S57" s="3">
-        <v>8300</v>
       </c>
       <c r="T57" s="3">
         <v>8300</v>
       </c>
       <c r="U57" s="3">
+        <v>8300</v>
+      </c>
+      <c r="V57" s="3">
         <v>8700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4653,8 +4784,8 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4662,41 +4793,44 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2700</v>
       </c>
       <c r="H58" s="3">
         <v>2700</v>
       </c>
       <c r="I58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J58" s="3">
         <v>2600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4751,8 +4885,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4762,66 +4899,66 @@
       <c r="E59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>400</v>
       </c>
       <c r="H59" s="3">
         <v>400</v>
       </c>
       <c r="I59" s="3">
+        <v>400</v>
+      </c>
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>45400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>36600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>30300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>32400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>31400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9900</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4831,8 +4968,8 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -4840,77 +4977,80 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E60" s="3">
         <v>49400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>52700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>66700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>54100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>43900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>28600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>23900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4920,8 +5060,8 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC60" s="3">
-        <v>0</v>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD60" s="3">
         <v>0</v>
@@ -4929,41 +5069,44 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E61" s="3">
         <v>38700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>40500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>43300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>44000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>44800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5018,77 +5161,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>48600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>46400</v>
       </c>
       <c r="O62" s="3">
         <v>46400</v>
       </c>
       <c r="P62" s="3">
+        <v>46400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>46500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>46100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3900</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5098,8 +5244,8 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5107,8 +5253,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5196,8 +5345,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5285,8 +5437,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5374,77 +5529,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E66" s="3">
         <v>88600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>93200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>96300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>109100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>98700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>114300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>98200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>100700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>95400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>60100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>60000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>57000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>52200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>44000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>27600</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5463,8 +5621,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5496,8 +5657,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5585,8 +5747,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5674,8 +5839,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5740,11 +5908,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>155900</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5763,8 +5931,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5852,77 +6023,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1129500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1102700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1054400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1006900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-966800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-878500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-888600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-827600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-772100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-659600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-596400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-541400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-487000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-418600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-359600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-309500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-305300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-250700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-200800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-160500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-126000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-99100</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5941,8 +6115,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6030,8 +6207,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6119,8 +6299,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6208,77 +6391,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E76" s="3">
         <v>295400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>337200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>354300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>382600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>458800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>437300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>481800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>523100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>385500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>433800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>428500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>472500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>315300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>364000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>393400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>223800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>268400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>308600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>341100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>213200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-95900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6288,8 +6474,8 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD76" s="3">
         <v>0</v>
@@ -6297,8 +6483,11 @@
       <c r="AE76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6386,85 +6575,88 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6480,80 +6672,83 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-48300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-88300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-60900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-55500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-112500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-63200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-55000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-68400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-59100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-50100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-54600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-49900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-40300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-34600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-26900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6569,8 +6764,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6602,8 +6800,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6620,7 +6819,7 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -6629,28 +6828,28 @@
         <v>400</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
       </c>
       <c r="O83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>300</v>
       </c>
       <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -6659,19 +6858,19 @@
         <v>100</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -6682,8 +6881,8 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -6691,8 +6890,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6780,8 +6982,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6869,8 +7074,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6958,8 +7166,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7047,8 +7258,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7136,77 +7350,80 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-39700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-44000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-35100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-52000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-40600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-38700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-79300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-49300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-33200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-43000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-33500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-46100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-37500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-27400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-20600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-22000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-16900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7216,8 +7433,8 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -7225,8 +7442,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7258,76 +7478,77 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-2700</v>
       </c>
       <c r="R91" s="3">
         <v>-2700</v>
       </c>
       <c r="S91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -7338,8 +7559,8 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7347,8 +7568,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7436,8 +7660,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7525,76 +7752,79 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E94" s="3">
         <v>40500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>32300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>48200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>34500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>61500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-117500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>72900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>42100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-142100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>43300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-141400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>66600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>13500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-137900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-137300</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -7605,8 +7835,8 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -7614,8 +7844,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7647,8 +7880,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7679,8 +7913,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7736,8 +7970,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7825,8 +8062,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7914,8 +8154,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8003,23 +8246,26 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -8027,53 +8273,53 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>236600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>49700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>209500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>12300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>166600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>155900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>191700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>13500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8083,8 +8329,8 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -8092,8 +8338,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8124,8 +8373,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8181,77 +8430,80 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>8000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-82700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-155800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>230300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-24000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-37600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>32400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8261,13 +8513,16 @@
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZNTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="92">
   <si>
     <t>ZNTL</t>
   </si>
@@ -656,126 +656,127 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
@@ -788,8 +789,14 @@
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -802,24 +809,24 @@
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>26900</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>40600</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,11 +839,11 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -883,8 +890,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -978,8 +991,14 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -992,24 +1011,24 @@
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>26900</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>40600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1073,8 +1092,14 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1108,89 +1133,91 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F12" s="3">
         <v>23000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>27600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>27200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>33000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>36800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>48400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>49600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>51600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>46800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>42700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>48600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>40600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>42200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>43800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>46100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>38400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>45200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>44800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>38400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>29500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>24700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>17500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>13300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>7100</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1203,8 +1230,14 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1298,8 +1331,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1307,59 +1346,59 @@
         <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>700</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>10500</v>
       </c>
-      <c r="G14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>22900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-4600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>45600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-42800</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1372,11 +1411,11 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1393,8 +1432,14 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1405,10 +1450,10 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
@@ -1429,14 +1474,14 @@
         <v>300</v>
       </c>
       <c r="N15" s="3">
+        <v>300</v>
+      </c>
+      <c r="O15" s="3">
+        <v>300</v>
+      </c>
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1488,8 +1533,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1520,89 +1571,91 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F17" s="3">
         <v>33700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>34900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>37800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>73000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>51400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>65100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>65300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>67900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>62700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>58300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>65000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>51800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>54200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>63500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>57900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>48200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>11300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>55100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>50300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>40200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>34800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>27400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>16400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8700</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1615,89 +1668,95 @@
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-33700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-34900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-37800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-46100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-51400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-65100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-24800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-67900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-62700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-58300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-65000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-63500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-57900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-48200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-11300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-55100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-50300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-40200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-34800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-27400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1710,8 +1769,14 @@
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1745,61 +1810,63 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-11200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>13700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
@@ -1808,25 +1875,25 @@
         <v>100</v>
       </c>
       <c r="W20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>200</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AB20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>100</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1840,89 +1907,95 @@
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-26500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-34700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-37600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-45800</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-39900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-64800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-24400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-67600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-62400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-71700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-66900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-62700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-57100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-47900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-11100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-54900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-50200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-39900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1935,8 +2008,14 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1973,11 +2052,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2030,89 +2109,95 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-26700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-26900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-48300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-47700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-40200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-88000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-61100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-55500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-113200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-63200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-48500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-52300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-63000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-57500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-48100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-11200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-55000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-50200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-39900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,103 +2210,115 @@
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-700</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
+      <c r="AC24" s="3">
+        <v>0</v>
       </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>0</v>
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2315,89 +2412,95 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-26700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-26900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-48300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-47500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-40200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-88300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-60900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-55500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-112600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-63300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-48200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-52100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-63100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-57500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-48300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-55100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-50400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-40400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-34700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2410,89 +2513,95 @@
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-26700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-26900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-48300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-47500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-40200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-88300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>10100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-60900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-55500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-112500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-63200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-55000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-68400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-59100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-50100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-4200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-54600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-49900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-40300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2614,14 @@
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2600,8 +2715,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2695,8 +2816,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2790,8 +2917,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2885,61 +3018,67 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="J32" s="3">
         <v>11200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>-13700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
@@ -2948,25 +3087,25 @@
         <v>-100</v>
       </c>
       <c r="W32" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-200</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AB32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-100</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -2980,89 +3119,95 @@
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-26700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-26900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-48300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-47500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-40200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-88300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>10100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-60900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-55500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-112500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-63200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-55000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-68400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-59100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-50100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-54600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-49900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-40300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,8 +3220,14 @@
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3170,89 +3321,95 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-26700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-26900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-48300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-47500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-40200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-88300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>10100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-60900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-55500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-112500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-63200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-55000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-68400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-59100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-50100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-54600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-49900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-40300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,94 +3422,100 @@
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3365,8 +3528,14 @@
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3400,8 +3569,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3435,86 +3606,88 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F41" s="3">
         <v>39100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>37600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>41900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>33900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>41300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>37000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>37600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>28000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>110800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>266600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>36300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>43100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>42600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>55100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>30600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>59700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>40800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>49200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>29000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>55000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>92600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>96000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>63700</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,83 +3703,89 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>209900</v>
+      </c>
+      <c r="F42" s="3">
         <v>241600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>265800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>290500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>337200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>349900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>389400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>451400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>454900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>405900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>286400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>356200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>394300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>379200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>400100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>258800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>280200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>326000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>201700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>269400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>283600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>274900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>137200</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3616,17 +3795,23 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3639,15 +3824,15 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>5000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3675,35 +3860,35 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>400</v>
-      </c>
-      <c r="X43" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
+      <c r="AA43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>100</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
@@ -3711,17 +3896,23 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>0</v>
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3758,11 +3949,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3815,8 +4006,14 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3853,160 +4050,172 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>14600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>12200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>12400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>11900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>10900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>8500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>7700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>6200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>5200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>5200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>0</v>
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>218100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>253200</v>
+      </c>
+      <c r="F46" s="3">
         <v>288300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>311600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>342900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>386100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>400300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>439600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>503800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>496700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>528300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>563900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>410200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>451900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>433900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>467600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>301300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>350800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>377600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>259400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>306400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>345100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>372700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>238500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>66000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="3">
-        <v>0</v>
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4040,33 +4249,33 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>18900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>21200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>28000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>30400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>35700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>37500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>39300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4079,11 +4288,11 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -4100,103 +4309,115 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F48" s="3">
         <v>33100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>34300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>35200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>37200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>38400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>38800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>40400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>41700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>42600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>43200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>44400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>50100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>50700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>51500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>52100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>52800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>3400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>3400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>3600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>2400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>2600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2800</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4213,10 +4434,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>3700</v>
@@ -4252,10 +4473,10 @@
         <v>3700</v>
       </c>
       <c r="U49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="V49" s="3">
-        <v>12500</v>
+        <v>3700</v>
       </c>
       <c r="W49" s="3">
         <v>12500</v>
@@ -4269,11 +4490,11 @@
       <c r="Z49" s="3">
         <v>12500</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
+      <c r="AA49" s="3">
+        <v>12500</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>12500</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
@@ -4281,17 +4502,23 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>0</v>
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4385,8 +4612,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4480,103 +4713,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F52" s="3">
         <v>5800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>5800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>6000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>8200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>9500</v>
       </c>
       <c r="K52" s="3">
         <v>9500</v>
       </c>
       <c r="L52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="M52" s="3">
+        <v>9500</v>
+      </c>
+      <c r="N52" s="3">
         <v>11100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>10500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>12100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>12400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>12900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>14600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>12800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>9700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>9100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>8500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>6100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>5600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>6300</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4670,86 +4915,92 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>253100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>289000</v>
+      </c>
+      <c r="F54" s="3">
         <v>327300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>351700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>384000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>430300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>450700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>491700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>557500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>551700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>585700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>621400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>489300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>539300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>529200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>567900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>405700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>454500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>435100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>284000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>328400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>365600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>393200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>257200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>87600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4765,8 +5016,14 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4800,8 +5057,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4835,145 +5094,153 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>20400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>14900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>14300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>12800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>9800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>12000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>13200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>8000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>8300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>8300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>8700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>4200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>0</v>
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F58" s="3">
         <v>3700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5025,240 +5292,258 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>45400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>44200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>36600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>30300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>32400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>31400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>25300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>24500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>19900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>18500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>11400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>9900</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>36600</v>
+      </c>
+      <c r="F60" s="3">
         <v>37200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>39000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>49400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>52700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>54900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>66700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>54800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>69400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>58900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>51800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>56400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>56600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>54100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>48600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>43500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>43900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>39400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>33600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>32800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>28600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>23900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>15600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>16900</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>0</v>
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F61" s="3">
         <v>36700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>37700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>38700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>39600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>40500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>41300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>42600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>43200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>43300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>44000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>44800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5310,8 +5595,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5322,91 +5613,97 @@
         <v>500</v>
       </c>
       <c r="F62" s="3">
+        <v>500</v>
+      </c>
+      <c r="G62" s="3">
+        <v>500</v>
+      </c>
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>48600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>46400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>46400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>46500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>46100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5500,8 +5797,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5595,8 +5898,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5690,86 +5999,92 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>72800</v>
+      </c>
+      <c r="F66" s="3">
         <v>74400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>77200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>88600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>93200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>96300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>109100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>98700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>114300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>103800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>98200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>103700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>105500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>100700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>95400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>90400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>90600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>41600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>60100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>60000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>57000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>52200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>44000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>27600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5785,8 +6100,14 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5820,8 +6141,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5915,8 +6238,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6010,8 +6339,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6082,14 +6417,14 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
         <v>155900</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>0</v>
-      </c>
       <c r="AC70" s="3">
         <v>0</v>
       </c>
@@ -6105,8 +6440,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6200,86 +6541,92 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1226800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1191500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1156200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1129500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1102700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1054400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1006900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-966800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-878500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-888600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-827600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-772100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-659600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-596400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-541400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-487000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-418600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-359600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-309500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-305300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-250700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-200800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-160500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-126000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-99100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6295,8 +6642,14 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6390,8 +6743,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6485,8 +6844,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6580,103 +6945,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>216200</v>
+      </c>
+      <c r="F76" s="3">
         <v>252900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>274500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>295400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>337200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>354300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>382600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>458800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>437300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>481800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>523100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>385500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>433800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>428500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>472500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>315300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>364000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>393400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>223800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>268400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>308600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>341100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>213200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-95900</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>0</v>
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6770,94 +7147,100 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6870,89 +7253,95 @@
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-26700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-26900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-48300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-47500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-40200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-88300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>10100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-60900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-55500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-112500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-63200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-55000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-54400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-68400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-59100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-50100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-54600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-49900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-40300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-26900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6965,8 +7354,14 @@
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7000,8 +7395,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7024,46 +7421,46 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
       </c>
       <c r="M83" s="3">
+        <v>400</v>
+      </c>
+      <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
@@ -7072,13 +7469,13 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -7086,17 +7483,23 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7190,8 +7593,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7285,8 +7694,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7380,8 +7795,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7475,8 +7896,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7570,103 +7997,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-27000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-34700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-32600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-39700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-44000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-35100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-52000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-40600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-38700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-79300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-49300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-37300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-33200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-43000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-50200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-37000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-33500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-46100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-37500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-27400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-20600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7700,13 +8139,15 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
@@ -7714,14 +8155,14 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -7730,55 +8171,55 @@
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
@@ -7786,17 +8227,23 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7890,8 +8337,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7985,85 +8438,91 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>32400</v>
+      </c>
+      <c r="F94" s="3">
         <v>28300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>30400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>40500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>32300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>48200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>34500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>61500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-42100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-117500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>72900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>42100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-11900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>20000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-142100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>19800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>43300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-141400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>66600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>13500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-9600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-137900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-137300</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
@@ -8071,17 +8530,23 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8115,8 +8580,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8153,11 +8620,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8210,8 +8677,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8305,8 +8778,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8400,8 +8879,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8495,103 +8980,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>236600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>49700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>209500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>12300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>166600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>155900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>191700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>13500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8628,11 +9125,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8685,99 +9182,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F102" s="3">
         <v>1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>8000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>9600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-82700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-155800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>230300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>24300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-29100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>18500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-8400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>20200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-24000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-37600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>32400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
